--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subject\PBLsax\-SchoolActPlatform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC89AB7-34CB-40A2-83A0-510597AEE307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5F520-4F71-4A50-9BAE-11E45B2E028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="2" xr2:uid="{1ACCA5E6-2984-4267-850E-A4BD19BC86B6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{1ACCA5E6-2984-4267-850E-A4BD19BC86B6}"/>
   </bookViews>
   <sheets>
     <sheet name="需求列表" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="活动管理核心功能" sheetId="3" r:id="rId3"/>
     <sheet name="活动报名与收藏" sheetId="4" r:id="rId4"/>
     <sheet name="评论互动与系统优化" sheetId="5" r:id="rId5"/>
+    <sheet name="资源搜索" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="455">
   <si>
     <t>分数</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -890,6 +891,1053 @@
   </si>
   <si>
     <t>1. 访问一个已结束的活动详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通用户正常报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名后个人信息录入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复报名拦截</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未登录报名拦截</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>名额已满拦截</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名截止时间已过</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名并发处理</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 普通用户登录
+2. 进入活动详情页
+3. 点击"立即报名"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户报名时需填写附加信息（如联系方式）
+2. 提交</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 已报名该活动
+2. 再次点击报名按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 未登录状态
+2. 点击"立即报名"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 活动设置限额，且已报满
+2. 用户尝试报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 当前时间超过活动报名截止时间
+2. 用户尝试报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 模拟多人同时报名同一活动（剩余1个名额）
+2. 并发请求</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"报名成功"，按钮变为"已报名"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名成功，管理员可看到附加信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"您已报名该活动"，不重复记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转登录页面，登录后返回活动详情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"名额已满，无法报名"，按钮置灰</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"报名已截止"，按钮不可点击</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>仅1人报名成功，其余提示"名额已满"，无超卖</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取消报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常取消报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取消后可重新报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>未报名用户无取消入口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动已开始不可取消</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名信息查看（管理员）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看报名名单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户已报名某活动
+2. 在详情页或"我的报名"中点击"取消报名"
+3. 确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 取消报名后刷新页面
+2. 重新点击"立即报名"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 未报名该活动
+2. 查看活动详情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 活动已开始
+2. 用户尝试取消报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"取消报名成功"，活动名额释放</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名成功，名额减1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>不显示"取消报名"按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"活动已开始，无法取消报名"或按钮隐藏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无报名者查看</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通用户无法查看</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>导出报名名单</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员登录
+2. 进入活动管理，点击某活动的"报名管理"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员查看无人报名的活动
+2. 点击"报名管理"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 普通用户登录
+2. 尝试访问管理员报名管理接口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员在报名管理页
+2. 点击"导出名单"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示报名人数统计、报名用户列表（学号/姓名/报名时间）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示"暂无报名"或空列表，人数为0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示无权限或403</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>下载Excel文件，包含报名用户信息</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人报名记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>关键词搜索</t>
+  </si>
+  <si>
+    <t>模糊关键词搜索</t>
+  </si>
+  <si>
+    <t>空关键词搜索</t>
+  </si>
+  <si>
+    <t>特殊字符搜索</t>
+  </si>
+  <si>
+    <t>无匹配结果</t>
+  </si>
+  <si>
+    <t>搜索词前后空格处理</t>
+  </si>
+  <si>
+    <t>大小写不敏感</t>
+  </si>
+  <si>
+    <t>按资源类型筛选</t>
+  </si>
+  <si>
+    <t>选择单一类型-视频</t>
+  </si>
+  <si>
+    <t>选择单一类型-文档</t>
+  </si>
+  <si>
+    <t>选择单一类型-音频</t>
+  </si>
+  <si>
+    <t>不选择类型（全部）</t>
+  </si>
+  <si>
+    <t>选择"初级"</t>
+  </si>
+  <si>
+    <t>选择"中级"</t>
+  </si>
+  <si>
+    <t>选择"高级"</t>
+  </si>
+  <si>
+    <t>不选择难度（全部）</t>
+  </si>
+  <si>
+    <t>按标签筛选</t>
+  </si>
+  <si>
+    <t>选择单个标签</t>
+  </si>
+  <si>
+    <t>选择多个标签(并集/交集)</t>
+  </si>
+  <si>
+    <t>取消已选标签</t>
+  </si>
+  <si>
+    <t>不选择标签（全部）</t>
+  </si>
+  <si>
+    <t>组合搜索</t>
+  </si>
+  <si>
+    <t>关键词+资源类型</t>
+  </si>
+  <si>
+    <t>关键词+难度级别</t>
+  </si>
+  <si>
+    <t>关键词+标签</t>
+  </si>
+  <si>
+    <t>类型+难度+标签（全组合）</t>
+  </si>
+  <si>
+    <t>搜索+全筛选条件无结果</t>
+  </si>
+  <si>
+    <t>搜索结果展示</t>
+  </si>
+  <si>
+    <t>搜索结果数量显示</t>
+  </si>
+  <si>
+    <t>搜索结果分页</t>
+  </si>
+  <si>
+    <t>搜索结果排序</t>
+  </si>
+  <si>
+    <t>搜索结果中资源详情入口</t>
+  </si>
+  <si>
+    <t>点击重置按钮</t>
+  </si>
+  <si>
+    <t>正常收藏活动</t>
+  </si>
+  <si>
+    <t>未登录收藏拦截</t>
+  </si>
+  <si>
+    <t>跳转登录页面</t>
+  </si>
+  <si>
+    <t>重复收藏幂等性</t>
+  </si>
+  <si>
+    <t>查看收藏列表</t>
+  </si>
+  <si>
+    <t>收藏列表联动取消收藏</t>
+  </si>
+  <si>
+    <t>收藏活动已删除处理</t>
+  </si>
+  <si>
+    <t>收藏功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"收藏成功"，图标变为已收藏状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>提示"已取消收藏"，图标恢复未收藏状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转登录页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据库不产生重复记录，状态不变</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示所有收藏活动，可按收藏时间排序</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>该活动从收藏列表消失</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>该活动不显示或标记"已失效"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>查看个人报名记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>报名记录包含状态</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取消后记录更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户已报名多个活动
+2. 进入"我的报名"页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户报名了已结束和进行中的活动
+2. 查看报名记录</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 取消某活动报名
+2. 返回"我的报名"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户登录
+2. 在活动详情页点击"收藏"图标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 已收藏某活动
+2. 再次点击"已收藏"图标</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取消收藏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 未登录
+2. 点击收藏按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 已收藏某活动
+2. 通过接口再次发送收藏请求</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户已收藏多个活动
+2. 进入"我的收藏"页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 在收藏列表点击"取消收藏"
+2. 刷新页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员删除了用户已收藏的活动
+2. 用户查看收藏列表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>该活动不再显示在报名列表中</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动状态正确标识（进行中/已结束/待开始）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示所有已报名活动，按报名时间倒序</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>评论发布</t>
+  </si>
+  <si>
+    <t>正常发表评论</t>
+  </si>
+  <si>
+    <t>评论立即出现在评论列表中，显示用户名、头像、时间</t>
+  </si>
+  <si>
+    <t>发表带表情评论</t>
+  </si>
+  <si>
+    <t>1. 输入评论内容含emoji表情</t>
+  </si>
+  <si>
+    <t>表情正常显示</t>
+  </si>
+  <si>
+    <t>空评论拦截</t>
+  </si>
+  <si>
+    <t>提示"评论内容不能为空"</t>
+  </si>
+  <si>
+    <t>超长评论处理</t>
+  </si>
+  <si>
+    <t>提示"评论不能超过500字"或自动截断</t>
+  </si>
+  <si>
+    <t>未登录评论拦截</t>
+  </si>
+  <si>
+    <t>敏感词过滤</t>
+  </si>
+  <si>
+    <t>提示"评论包含不当内容"或自动替换为*</t>
+  </si>
+  <si>
+    <t>评论展示</t>
+  </si>
+  <si>
+    <t>评论列表正确展示</t>
+  </si>
+  <si>
+    <t>评论按时间倒序排列，显示用户、内容、时间</t>
+  </si>
+  <si>
+    <t>无评论活动展示</t>
+  </si>
+  <si>
+    <t>显示"暂无评论，快来发表第一条评论吧"</t>
+  </si>
+  <si>
+    <t>评论分页加载</t>
+  </si>
+  <si>
+    <t>自动加载更多评论或显示"加载更多"按钮</t>
+  </si>
+  <si>
+    <t>用户本人评论标识</t>
+  </si>
+  <si>
+    <t>自己评论有特殊标识（如颜色区分），可显示"删除"按钮</t>
+  </si>
+  <si>
+    <t>评论管理</t>
+  </si>
+  <si>
+    <t>管理员删除不当评论</t>
+  </si>
+  <si>
+    <t>评论被删除，提示"删除成功"</t>
+  </si>
+  <si>
+    <t>用户删除自己评论</t>
+  </si>
+  <si>
+    <t>评论被删除，评论区更新</t>
+  </si>
+  <si>
+    <t>用户无法删除他人评论</t>
+  </si>
+  <si>
+    <t>不显示"删除"按钮或接口拒绝</t>
+  </si>
+  <si>
+    <t>删除后数据更新</t>
+  </si>
+  <si>
+    <t>评论总数减1，该评论内容不再显示</t>
+  </si>
+  <si>
+    <t>系统性能优化</t>
+  </si>
+  <si>
+    <t>首页加载性能</t>
+  </si>
+  <si>
+    <t>页面完全加载时间≤2秒</t>
+  </si>
+  <si>
+    <t>活动列表大数据量性能</t>
+  </si>
+  <si>
+    <t>首次加载≤2秒，滚动流畅无卡顿</t>
+  </si>
+  <si>
+    <t>活动详情页图片懒加载</t>
+  </si>
+  <si>
+    <t>图片采用懒加载，首屏加载不受图片影响</t>
+  </si>
+  <si>
+    <t>缓存命中验证</t>
+  </si>
+  <si>
+    <t>第二次加载明显快于首次（缓存生效）</t>
+  </si>
+  <si>
+    <t>高并发报名压力测试</t>
+  </si>
+  <si>
+    <t>无请求失败，名额扣减无误，平均响应时间≤1秒</t>
+  </si>
+  <si>
+    <t>响应式设计</t>
+  </si>
+  <si>
+    <t>PC端布局</t>
+  </si>
+  <si>
+    <t>布局合理，元素无错位重叠</t>
+  </si>
+  <si>
+    <t>平板端布局</t>
+  </si>
+  <si>
+    <t>菜单缩为汉堡图标，内容区域自适应</t>
+  </si>
+  <si>
+    <t>手机端布局</t>
+  </si>
+  <si>
+    <t>单列布局，按钮可点击区域≥44px，无横向滚动条</t>
+  </si>
+  <si>
+    <t>横竖屏切换</t>
+  </si>
+  <si>
+    <t>页面布局自动适配，内容不丢失不错位</t>
+  </si>
+  <si>
+    <t>集成测试</t>
+  </si>
+  <si>
+    <t>端到端全流程</t>
+  </si>
+  <si>
+    <t>全流程顺畅，数据一致，权限验证正确</t>
+  </si>
+  <si>
+    <t>异常操作恢复</t>
+  </si>
+  <si>
+    <t>未提交数据丢失（预期），已提交数据持久化成功</t>
+  </si>
+  <si>
+    <t>浏览器兼容性</t>
+  </si>
+  <si>
+    <t>三个浏览器表现一致，无样式或功能异常</t>
+  </si>
+  <si>
+    <t>安全性基础测试</t>
+  </si>
+  <si>
+    <t>SQL注入无效；脚本被转义，不执行；密码等敏感信息加密传输</t>
+  </si>
+  <si>
+    <t>1. 尝试SQL注入（输入特殊字符）
+2. 尝试XSS（输入脚本标签）
+3. 抓包查看敏感数据传输</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 分别在Chrome、Firefox、Edge最新版
+2. 执行核心功能</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 操作中途断开网络
+2. 恢复网络后刷新页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员发布活动
+2. 普通用户注册→登录
+3. 浏览活动列表→筛选
+4. 查看详情→报名→收藏→评论
+5. 管理员查看报名→删除评论
+6. 用户查看报名记录→取消报名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 手机端打开活动详情
+2. 旋转屏幕切换横竖屏</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. iPhone尺寸390x844
+2. 访问主要页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. iPad尺寸768x1024
+2. 访问主要页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Chrome浏览器1920x1080
+2. 访问首页、活动列表、活动详情</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 使用压测工具
+2. 模拟100用户同时报名
+3. 观察系统响应</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 首次访问某页面
+2. 再次访问同一页面</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 活动有多张高清图片
+2. 打开详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 系统中存在200+活动
+2. 访问活动列表页
+3. 记录加载时间</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 清除浏览器缓存
+2. 使用开发者工具记录加载时间
+3. 访问系统首页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员删除一条评论
+2. 刷新活动详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 普通用户登录
+2. 查看他人评论</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 普通用户登录
+2. 在自己发表的评论上点击"删除"
+3. 确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 管理员登录
+2. 查看活动评论列表
+3. 点击某评论的"删除"
+4. 确认</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 登录用户查看自己发表的评论
+2. 对比他人评论</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 评论超过20条
+2. 滑动到评论区底部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 活动暂无评论
+2. 打开详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 活动有多条评论
+2. 打开活动详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入包含敏感词的评论
+2. 点击发表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 未登录状态
+2. 点击评论发表按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入超过500字的评论
+2. 发表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 不输入任何内容
+2. 点击发表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入评论内容含emoji表情
+2. 发表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 用户登录
+2. 进入活动详情页评论区
+3. 输入评论内容
+4. 点击"发表"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回标题或描述包含"Python入门教程"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回所有包含"Python"的资源（如Python入门、Python进阶等）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示全部资源或提示"请输入搜索关键词"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统正常处理，提示"未找到相关资源"或返回匹配结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示"未找到相关资源"或空结果页，给出搜索建议</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动去除首尾空格，正常搜索"Python"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>能搜索到标题含"Python"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示类型为"视频"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示类型为"文档"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示类型为"音频"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回所有类型的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示难度为"初级"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示难度为"中级"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示难度为"高级"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回所有难度的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>只显示包含"机器学习"标签的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>根据系统逻辑：显示同时满足或任一满足的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>搜索结果不再受该标签限制</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回所有标签的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回类型为"视频"且包含"Python"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回难度为"初级"且包含"机器学习"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回含"Python"标签且匹配"数据分析"的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回同时满足三个条件的资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示"未找到相关资源"，建议放宽条件</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>显示"共找到X个资源"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>正常加载后续结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>列表按所选排序正确排列</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳转到资源详情页</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有条件清空，恢复默认显示全部资源</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>重置搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>精确关键词搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 设置多个搜索条件
+2. 点击"重置"</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 在搜索结果列表
+2. 点击某资源标题</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 执行搜索
+2. 切换排序方式（按时间/相关度/热度）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 搜索结果超过单页数量
+2. 点击下一页或滚动</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 执行搜索
+2. 查看页面顶部或底部</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入关键词+多个筛选条件
+2. 条件组合无匹配结果</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择类型"视频"
+2. 选择难度"中级"
+3. 选择标签"深度学习"
+4. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入"数据分析"
+2. 选择标签"Python"
+3. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入"机器学习"
+2. 选择难度"初级"
+3. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入"Python"
+2. 选择类型"视频"
+3. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 标签不选
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 已选"机器学习"
+2. 再次点击取消选择
+3. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 同时勾选"机器学习"和"Python"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择标签"机器学习"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 难度级别选择"全部"或不选
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择难度"高级"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择难度"中级"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择难度级别"初级"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 资源类型选择"全部"或不选
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择类型"音频"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 选择类型"文档"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 在筛选条件中选择类型"视频"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入"python"（全小写）
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入" Python "（前后有空格）
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入不存在的关键词"xyz123不存在"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入"@#$%"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 关键词留空
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 输入关键词"Python"
+2. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 进入资源搜索页面
+2. 输入完整关键词"Python入门教程"
+3. 点击搜索</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1038,7 +2086,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,9 +2114,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1084,14 +2129,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1126,11 +2165,23 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1466,10 +2517,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="30">
         <v>25</v>
       </c>
       <c r="C2" t="s">
@@ -1477,22 +2528,22 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="9"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="30"/>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15"/>
-      <c r="B4" s="9"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="30"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15"/>
-      <c r="B5" s="9">
+      <c r="A5" s="29"/>
+      <c r="B5" s="30">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -1500,16 +2551,16 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15"/>
-      <c r="B6" s="9"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="30"/>
     </row>
     <row r="7" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15"/>
-      <c r="B7" s="9"/>
+      <c r="A7" s="29"/>
+      <c r="B7" s="30"/>
     </row>
     <row r="8" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15"/>
-      <c r="B8" s="9">
+      <c r="A8" s="29"/>
+      <c r="B8" s="30">
         <v>21</v>
       </c>
       <c r="C8" t="s">
@@ -1518,14 +2569,14 @@
     </row>
     <row r="9" spans="1:3" ht="2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="9"/>
+      <c r="B9" s="30"/>
     </row>
     <row r="10" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="9"/>
+      <c r="B10" s="30"/>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="29" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="2">
@@ -1536,8 +2587,8 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="9">
+      <c r="A12" s="29"/>
+      <c r="B12" s="30">
         <v>16</v>
       </c>
       <c r="C12" t="s">
@@ -1545,21 +2596,21 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15"/>
-      <c r="B13" s="9"/>
+      <c r="A13" s="29"/>
+      <c r="B13" s="30"/>
       <c r="C13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="9"/>
+      <c r="A14" s="29"/>
+      <c r="B14" s="30"/>
       <c r="C14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="29" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
@@ -1570,73 +2621,73 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="13"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="12"/>
       <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="15"/>
-      <c r="B17" s="13"/>
+      <c r="A17" s="29"/>
+      <c r="B17" s="12"/>
       <c r="C17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="13"/>
+      <c r="A18" s="29"/>
+      <c r="B18" s="12"/>
       <c r="C18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="15"/>
-      <c r="B19" s="14"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="13"/>
       <c r="C19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="14"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="13"/>
       <c r="C20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="B21" s="14"/>
+      <c r="B21" s="13"/>
       <c r="C21" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="15"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="29"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="15"/>
-      <c r="B23" s="14"/>
+      <c r="A23" s="29"/>
+      <c r="B23" s="13"/>
       <c r="C23" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="15"/>
-      <c r="B24" s="14"/>
+      <c r="A24" s="29"/>
+      <c r="B24" s="13"/>
       <c r="C24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="15"/>
-      <c r="B25" s="14"/>
+      <c r="A25" s="29"/>
+      <c r="B25" s="13"/>
       <c r="C25" t="s">
         <v>29</v>
       </c>
@@ -1694,17 +2745,17 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="19" t="s">
+      <c r="B2" s="15"/>
+      <c r="C2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="17">
         <v>5</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="15" t="s">
         <v>99</v>
       </c>
       <c r="F2" s="5" t="s">
@@ -1712,394 +2763,394 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="28"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="17">
         <v>3</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="18" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="17">
         <v>5</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="23" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="17">
         <v>5</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="18" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="17">
         <v>4</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="9" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="18" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="17">
         <v>5</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="18" t="s">
+      <c r="A8" s="27"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="17">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="9" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18" t="s">
+      <c r="A9" s="27"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="17">
         <v>4</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="9" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18" t="s">
+      <c r="A10" s="27"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="17">
         <v>3</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="9" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="18" t="s">
+      <c r="A11" s="27"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="17">
         <v>4</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18" t="s">
+      <c r="B12" s="15"/>
+      <c r="C12" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="17">
         <v>5</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="19" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="17">
         <v>4</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="18" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="17">
         <v>4</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="F14" s="10" t="s">
+      <c r="F14" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="21"/>
-      <c r="C15" s="18" t="s">
+      <c r="A15" s="28"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="17">
         <v>4</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="9" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="17">
         <v>5</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="17">
         <v>3</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="9" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="21"/>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="18"/>
+      <c r="C18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="20">
+      <c r="D18" s="17">
         <v>3</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="10" t="s">
+      <c r="F18" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="18" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="20">
+      <c r="D19" s="17">
         <v>4</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="9" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="18" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="17">
         <v>5</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="F20" s="10" t="s">
+      <c r="F20" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="17"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="18" t="s">
+      <c r="A21" s="28"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="17">
         <v>4</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="15" t="s">
         <v>118</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="21"/>
-      <c r="C22" s="19" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="17">
         <v>3</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="15" t="s">
         <v>119</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="19" t="s">
+      <c r="A23" s="28"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="17">
         <v>5</v>
       </c>
-      <c r="E23" s="18" t="s">
+      <c r="E23" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="9" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="17"/>
-      <c r="B24" s="21"/>
-      <c r="C24" s="19" t="s">
+      <c r="A24" s="28"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="17">
         <v>5</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="F24" s="10" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="18" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="17">
         <v>4</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="9" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="19" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="17">
         <v>5</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="10" t="s">
+      <c r="F26" s="9" t="s">
         <v>146</v>
       </c>
     </row>
@@ -2131,539 +3182,539 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="25" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="25" t="s">
+      <c r="G1" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="24"/>
-    </row>
-    <row r="2" spans="1:8" ht="93" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D2" s="29">
+      <c r="D2" s="19">
         <v>5</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="19" t="s">
+      <c r="A3" s="27"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="D3" s="29">
+      <c r="D3" s="19">
         <v>4</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="19" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="19">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="19" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="19">
         <v>3</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="19" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D6" s="29">
+      <c r="D6" s="19">
         <v>3</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="19" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D7" s="29">
+      <c r="D7" s="19">
         <v>5</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="19" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="19">
         <v>5</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E8" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="27"/>
-      <c r="H8" s="27"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="17"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="28"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="26">
         <v>4</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="19" t="s">
+      <c r="A10" s="28"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="19">
         <v>5</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D11" s="29">
+      <c r="D11" s="19">
         <v>5</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="19" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="19">
         <v>4</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="19" t="s">
+      <c r="A13" s="28"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="29">
+      <c r="D13" s="19">
         <v>3</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="17"/>
-      <c r="B14" s="21"/>
-      <c r="C14" s="19" t="s">
+      <c r="A14" s="28"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="19">
         <v>5</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B15" s="21"/>
-      <c r="C15" s="19" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="19">
         <v>5</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
-      <c r="B16" s="21"/>
-      <c r="C16" s="19" t="s">
+      <c r="A16" s="28"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="19">
         <v>4</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="17"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="19" t="s">
+      <c r="A17" s="28"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="D17" s="29">
+      <c r="D17" s="19">
         <v>4</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="G17" s="27"/>
-      <c r="H17" s="27"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="17"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="19" t="s">
+      <c r="A18" s="28"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="29">
+      <c r="D18" s="19">
         <v>4</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="19" t="s">
+      <c r="A19" s="28"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="19">
         <v>3</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="G19" s="27"/>
-      <c r="H19" s="27"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A20" s="17"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="19" t="s">
+      <c r="A20" s="28"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="D20" s="29">
+      <c r="D20" s="19">
         <v>3</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="21"/>
-      <c r="C21" s="19" t="s">
+      <c r="B21" s="18"/>
+      <c r="C21" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="19">
         <v>5</v>
       </c>
-      <c r="E21" s="18" t="s">
+      <c r="E21" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
     </row>
     <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="17"/>
-      <c r="B22" s="21"/>
-      <c r="C22" s="19" t="s">
+      <c r="A22" s="28"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="19">
         <v>3</v>
       </c>
-      <c r="E22" s="18" t="s">
+      <c r="E22" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="19" t="s">
+      <c r="A23" s="28"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="19">
         <v>3</v>
       </c>
-      <c r="E23" s="23" t="s">
+      <c r="E23" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="21"/>
-      <c r="C24" s="19" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="19">
         <v>4</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="19" t="s">
+      <c r="A25" s="28"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="19">
         <v>3</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
     </row>
     <row r="26" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="21"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
+      <c r="A26" s="18"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
     </row>
     <row r="27" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
     </row>
     <row r="28" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
+      <c r="A28" s="24"/>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
     </row>
     <row r="29" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
     </row>
     <row r="30" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
+      <c r="A30" s="24"/>
+      <c r="B30" s="24"/>
+      <c r="C30" s="24"/>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
     </row>
     <row r="31" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A24:A25"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A20"/>
     <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A24:A25"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2672,12 +3723,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F4FCE2-633D-47A2-8D27-A87BEF2998A9}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" customWidth="1"/>
     <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="5" max="5" width="38.58203125" customWidth="1"/>
+    <col min="6" max="6" width="39.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -2702,7 +3755,398 @@
       </c>
       <c r="H1" s="3"/>
     </row>
+    <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="31"/>
+      <c r="C3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="31"/>
+      <c r="C4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="C5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D5">
+        <v>5</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="C6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="C7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A8" s="31"/>
+      <c r="C8" t="s">
+        <v>201</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="C9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="F9" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="C10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
+      <c r="C11" t="s">
+        <v>219</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A12" s="31"/>
+      <c r="C12" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F12" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="F13" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="C14" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14">
+        <v>3</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="C16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A17" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="C17" t="s">
+        <v>291</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="F17" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="C18" t="s">
+        <v>292</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F18" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A19" s="31"/>
+      <c r="C19" t="s">
+        <v>293</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="F19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A20" s="29" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
+        <v>276</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="F20" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A21" s="29"/>
+      <c r="C21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D21">
+        <v>4</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="F21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A22" s="29"/>
+      <c r="C22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="F22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A23" s="29"/>
+      <c r="C23" t="s">
+        <v>279</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="F23" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A24" s="29"/>
+      <c r="C24" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="F24" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A25" s="29"/>
+      <c r="C25" t="s">
+        <v>281</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="F25" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>282</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="F26" t="s">
+        <v>290</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A8"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2710,18 +4154,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4A5F92B-A300-4654-91A6-5DBECE4114A9}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="22.5" customWidth="1"/>
     <col min="3" max="3" width="16.6640625" customWidth="1"/>
     <col min="4" max="4" width="15.58203125" customWidth="1"/>
-    <col min="5" max="5" width="14.4140625" customWidth="1"/>
-    <col min="6" max="6" width="16.9140625" customWidth="1"/>
+    <col min="5" max="5" width="34.83203125" customWidth="1"/>
+    <col min="6" max="6" width="57" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>63</v>
+        <v>7</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="6" t="s">
@@ -2741,7 +4186,931 @@
       </c>
       <c r="H1" s="3"/>
     </row>
+    <row r="2" spans="1:8" ht="56" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="31"/>
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>393</v>
+      </c>
+      <c r="F3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="31"/>
+      <c r="B4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="F4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="B5" t="s">
+        <v>316</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="F5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="B6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="B7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>389</v>
+      </c>
+      <c r="F7" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A8" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8">
+        <v>5</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="F8" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
+      <c r="B9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D9">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="F9" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="B10" t="s">
+        <v>326</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="F10" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A11" s="31"/>
+      <c r="B11" t="s">
+        <v>328</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F11" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="56" x14ac:dyDescent="0.3">
+      <c r="A12" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>331</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="F12" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" t="s">
+        <v>333</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="F13" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" t="s">
+        <v>335</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="F14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="B15" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F15" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="A16" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" t="s">
+        <v>340</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>380</v>
+      </c>
+      <c r="F16" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A17" s="31"/>
+      <c r="B17" t="s">
+        <v>342</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="F17" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="B18" t="s">
+        <v>344</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="F18" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A19" s="31"/>
+      <c r="B19" t="s">
+        <v>346</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="F19" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A20" s="31"/>
+      <c r="B20" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="F20" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A21" s="31" t="s">
+        <v>350</v>
+      </c>
+      <c r="B21" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="F21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A22" s="31"/>
+      <c r="B22" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="F22" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A23" s="31"/>
+      <c r="B23" t="s">
+        <v>355</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="F23" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A24" s="31"/>
+      <c r="B24" t="s">
+        <v>357</v>
+      </c>
+      <c r="D24">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="F24" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="168" x14ac:dyDescent="0.3">
+      <c r="A25" s="31" t="s">
+        <v>359</v>
+      </c>
+      <c r="B25" t="s">
+        <v>360</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="F25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="56" x14ac:dyDescent="0.3">
+      <c r="A26" s="31"/>
+      <c r="B26" t="s">
+        <v>362</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="56" x14ac:dyDescent="0.3">
+      <c r="A27" s="31"/>
+      <c r="B27" t="s">
+        <v>364</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F27" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="98" x14ac:dyDescent="0.3">
+      <c r="A28" s="31"/>
+      <c r="B28" t="s">
+        <v>366</v>
+      </c>
+      <c r="D28">
+        <v>4</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="F28" t="s">
+        <v>367</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="A25:A28"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A20"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F28461A-81FC-4C45-97A2-B9AEB4AC09F4}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.4140625" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="19.25" customWidth="1"/>
+    <col min="5" max="5" width="39.33203125" customWidth="1"/>
+    <col min="6" max="6" width="58" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="3"/>
+    </row>
+    <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
+      <c r="A2" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="F2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A3" s="31"/>
+      <c r="C3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="F3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A4" s="31"/>
+      <c r="C4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A5" s="31"/>
+      <c r="C5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A6" s="31"/>
+      <c r="C6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="F6" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A7" s="31"/>
+      <c r="C7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="F7" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A8" s="31"/>
+      <c r="C8" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="F8" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A9" s="31"/>
+      <c r="C9" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>447</v>
+      </c>
+      <c r="F9" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A10" s="31"/>
+      <c r="C10" t="s">
+        <v>252</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="F10" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A11" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="F11" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A12" s="31"/>
+      <c r="C12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D12">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="F12" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="C13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="C14" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>442</v>
+      </c>
+      <c r="F14" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="C15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="F15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="C16" t="s">
+        <v>258</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="F16" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A17" s="31"/>
+      <c r="C17" t="s">
+        <v>260</v>
+      </c>
+      <c r="D17">
+        <v>5</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="F17" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A18" s="31"/>
+      <c r="C18" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18">
+        <v>4</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="F18" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A19" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" t="s">
+        <v>262</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="F19" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A20" s="31"/>
+      <c r="C20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="F20" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A21" s="31"/>
+      <c r="C21" t="s">
+        <v>265</v>
+      </c>
+      <c r="D21">
+        <v>5</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="F21" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A22" s="31"/>
+      <c r="C22" t="s">
+        <v>266</v>
+      </c>
+      <c r="D22">
+        <v>4</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="F22" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" t="s">
+        <v>267</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F23" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="56" x14ac:dyDescent="0.3">
+      <c r="A24" s="31"/>
+      <c r="C24" t="s">
+        <v>268</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F24" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A25" s="31"/>
+      <c r="C25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="F25" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A26" s="31"/>
+      <c r="C26" t="s">
+        <v>271</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="F26" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A27" s="31"/>
+      <c r="C27" t="s">
+        <v>272</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="F27" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A28" s="31" t="s">
+        <v>270</v>
+      </c>
+      <c r="C28" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F28" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A29" s="31"/>
+      <c r="C29" t="s">
+        <v>274</v>
+      </c>
+      <c r="D29">
+        <v>4</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="F29" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A30" s="31"/>
+      <c r="C30" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30">
+        <v>3</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="F30" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="31"/>
+      <c r="C31" t="s">
+        <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:A10"/>
+    <mergeCell ref="A11:A18"/>
+    <mergeCell ref="A19:A22"/>
+    <mergeCell ref="A23:A27"/>
+    <mergeCell ref="A28:A31"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subject\PBLsax\-SchoolActPlatform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE5F520-4F71-4A50-9BAE-11E45B2E028D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4685AEAB-3BA2-4F72-AD56-88BEADB0B380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{1ACCA5E6-2984-4267-850E-A4BD19BC86B6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="454">
   <si>
     <t>分数</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1119,13 +1119,7 @@
     <t>特殊字符搜索</t>
   </si>
   <si>
-    <t>无匹配结果</t>
-  </si>
-  <si>
     <t>搜索词前后空格处理</t>
-  </si>
-  <si>
-    <t>大小写不敏感</t>
   </si>
   <si>
     <t>按资源类型筛选</t>
@@ -1347,9 +1341,6 @@
   </si>
   <si>
     <t>发表带表情评论</t>
-  </si>
-  <si>
-    <t>1. 输入评论内容含emoji表情</t>
   </si>
   <si>
     <t>表情正常显示</t>
@@ -1940,12 +1931,52 @@
 3. 点击搜索</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>大小写不敏感</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>无匹配结果(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>无法一眼知其含义，不符合所给出的用例规范</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2051,6 +2082,22 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2086,7 +2133,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2168,10 +2215,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -2180,8 +2224,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2517,10 +2567,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="30">
+      <c r="B2" s="29">
         <v>25</v>
       </c>
       <c r="C2" t="s">
@@ -2528,22 +2578,22 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="29"/>
-      <c r="B3" s="30"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="29"/>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="29"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
-      <c r="B5" s="30">
+      <c r="A5" s="28"/>
+      <c r="B5" s="29">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -2551,16 +2601,16 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="29"/>
-      <c r="B6" s="30"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="29"/>
     </row>
     <row r="7" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="29"/>
     </row>
     <row r="8" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="29"/>
-      <c r="B8" s="30">
+      <c r="A8" s="28"/>
+      <c r="B8" s="29">
         <v>21</v>
       </c>
       <c r="C8" t="s">
@@ -2569,14 +2619,14 @@
     </row>
     <row r="9" spans="1:3" ht="2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="30"/>
+      <c r="B9" s="29"/>
     </row>
     <row r="10" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="30"/>
+      <c r="B10" s="29"/>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="2">
@@ -2587,8 +2637,8 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
-      <c r="B12" s="30">
+      <c r="A12" s="28"/>
+      <c r="B12" s="29">
         <v>16</v>
       </c>
       <c r="C12" t="s">
@@ -2596,21 +2646,21 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="29"/>
       <c r="C13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="29"/>
       <c r="C14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
@@ -2621,42 +2671,42 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="29"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="12"/>
       <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="29"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="12"/>
       <c r="C17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
+      <c r="A18" s="28"/>
       <c r="B18" s="12"/>
       <c r="C18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="29"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="13"/>
       <c r="C19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="13"/>
       <c r="C20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="13"/>
@@ -2665,28 +2715,28 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
+      <c r="A23" s="28"/>
       <c r="B23" s="13"/>
       <c r="C23" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="29"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="13"/>
       <c r="C24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
+      <c r="A25" s="28"/>
       <c r="B25" s="13"/>
       <c r="C25" t="s">
         <v>29</v>
@@ -2745,7 +2795,7 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="15"/>
@@ -2763,7 +2813,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
+      <c r="A3" s="30"/>
       <c r="B3" s="18"/>
       <c r="C3" s="16" t="s">
         <v>36</v>
@@ -2779,7 +2829,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="31" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
@@ -2797,7 +2847,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="18"/>
       <c r="C5" s="20" t="s">
         <v>38</v>
@@ -2813,7 +2863,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="18"/>
       <c r="C6" s="15" t="s">
         <v>39</v>
@@ -2829,7 +2879,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="18"/>
       <c r="C7" s="15" t="s">
         <v>40</v>
@@ -2845,7 +2895,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
+      <c r="A8" s="31"/>
       <c r="B8" s="18"/>
       <c r="C8" s="15" t="s">
         <v>41</v>
@@ -2861,7 +2911,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
+      <c r="A9" s="31"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
         <v>42</v>
@@ -2877,7 +2927,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+      <c r="A10" s="31"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15" t="s">
         <v>43</v>
@@ -2893,7 +2943,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
+      <c r="A11" s="31"/>
       <c r="B11" s="18"/>
       <c r="C11" s="15" t="s">
         <v>44</v>
@@ -2909,7 +2959,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="30" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="15"/>
@@ -2927,7 +2977,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="18"/>
       <c r="C13" s="16" t="s">
         <v>60</v>
@@ -2943,7 +2993,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="18"/>
       <c r="C14" s="15" t="s">
         <v>45</v>
@@ -2959,7 +3009,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="18"/>
       <c r="C15" s="15" t="s">
         <v>46</v>
@@ -2975,7 +3025,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="18"/>
       <c r="C16" s="15" t="s">
         <v>47</v>
@@ -2991,7 +3041,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="18"/>
       <c r="C17" s="16" t="s">
         <v>48</v>
@@ -3007,7 +3057,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="30" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="18"/>
@@ -3025,7 +3075,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="18"/>
       <c r="C19" s="15" t="s">
         <v>51</v>
@@ -3041,7 +3091,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="18"/>
       <c r="C20" s="15" t="s">
         <v>52</v>
@@ -3057,7 +3107,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="18"/>
       <c r="C21" s="15" t="s">
         <v>53</v>
@@ -3073,7 +3123,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="30" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18"/>
@@ -3091,7 +3141,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="18"/>
       <c r="C23" s="16" t="s">
         <v>56</v>
@@ -3107,7 +3157,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="18"/>
       <c r="C24" s="16" t="s">
         <v>57</v>
@@ -3123,7 +3173,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="18"/>
       <c r="C25" s="15" t="s">
         <v>58</v>
@@ -3204,7 +3254,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="31" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="18"/>
@@ -3224,7 +3274,7 @@
       <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
+      <c r="A3" s="31"/>
       <c r="B3" s="18"/>
       <c r="C3" s="16" t="s">
         <v>71</v>
@@ -3242,7 +3292,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
+      <c r="A4" s="31"/>
       <c r="B4" s="18"/>
       <c r="C4" s="16" t="s">
         <v>72</v>
@@ -3260,7 +3310,7 @@
       <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
+      <c r="A5" s="31"/>
       <c r="B5" s="18"/>
       <c r="C5" s="16" t="s">
         <v>73</v>
@@ -3278,7 +3328,7 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
+      <c r="A6" s="31"/>
       <c r="B6" s="18"/>
       <c r="C6" s="16" t="s">
         <v>74</v>
@@ -3296,7 +3346,7 @@
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
+      <c r="A7" s="31"/>
       <c r="B7" s="18"/>
       <c r="C7" s="16" t="s">
         <v>75</v>
@@ -3314,7 +3364,7 @@
       <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.3">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="30" t="s">
         <v>76</v>
       </c>
       <c r="B8" s="18"/>
@@ -3334,7 +3384,7 @@
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="18"/>
       <c r="C9" s="20" t="s">
         <v>78</v>
@@ -3352,7 +3402,7 @@
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
+      <c r="A10" s="30"/>
       <c r="B10" s="18"/>
       <c r="C10" s="16" t="s">
         <v>79</v>
@@ -3370,7 +3420,7 @@
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="30" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="18"/>
@@ -3390,7 +3440,7 @@
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
+      <c r="A12" s="30"/>
       <c r="B12" s="18"/>
       <c r="C12" s="16" t="s">
         <v>82</v>
@@ -3408,7 +3458,7 @@
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
+      <c r="A13" s="30"/>
       <c r="B13" s="18"/>
       <c r="C13" s="16" t="s">
         <v>83</v>
@@ -3426,7 +3476,7 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
+      <c r="A14" s="30"/>
       <c r="B14" s="18"/>
       <c r="C14" s="16" t="s">
         <v>84</v>
@@ -3444,7 +3494,7 @@
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="30" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="18"/>
@@ -3464,7 +3514,7 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="18"/>
       <c r="C16" s="16" t="s">
         <v>87</v>
@@ -3482,7 +3532,7 @@
       <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="18"/>
       <c r="C17" s="16" t="s">
         <v>88</v>
@@ -3500,7 +3550,7 @@
       <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="18"/>
       <c r="C18" s="16" t="s">
         <v>89</v>
@@ -3518,7 +3568,7 @@
       <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="18"/>
       <c r="C19" s="16" t="s">
         <v>90</v>
@@ -3536,7 +3586,7 @@
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="18"/>
       <c r="C20" s="16" t="s">
         <v>91</v>
@@ -3554,7 +3604,7 @@
       <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="30" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="18"/>
@@ -3574,7 +3624,7 @@
       <c r="H21" s="24"/>
     </row>
     <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="18"/>
       <c r="C22" s="16" t="s">
         <v>94</v>
@@ -3592,7 +3642,7 @@
       <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="18"/>
       <c r="C23" s="16" t="s">
         <v>95</v>
@@ -3610,7 +3660,7 @@
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="30" t="s">
         <v>96</v>
       </c>
       <c r="B24" s="18"/>
@@ -3630,7 +3680,7 @@
       <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="18"/>
       <c r="C25" s="16" t="s">
         <v>98</v>
@@ -3756,7 +3806,7 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>194</v>
       </c>
       <c r="C2" t="s">
@@ -3773,7 +3823,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="27"/>
       <c r="C3" t="s">
         <v>196</v>
       </c>
@@ -3788,7 +3838,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="27"/>
       <c r="C4" t="s">
         <v>197</v>
       </c>
@@ -3803,7 +3853,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="27"/>
       <c r="C5" t="s">
         <v>198</v>
       </c>
@@ -3818,7 +3868,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="27"/>
       <c r="C6" t="s">
         <v>199</v>
       </c>
@@ -3833,7 +3883,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="27"/>
       <c r="C7" t="s">
         <v>200</v>
       </c>
@@ -3848,7 +3898,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
+      <c r="A8" s="27"/>
       <c r="C8" t="s">
         <v>201</v>
       </c>
@@ -3863,7 +3913,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="27" t="s">
         <v>216</v>
       </c>
       <c r="C9" t="s">
@@ -3880,7 +3930,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="27"/>
       <c r="C10" t="s">
         <v>218</v>
       </c>
@@ -3895,7 +3945,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
+      <c r="A11" s="27"/>
       <c r="C11" t="s">
         <v>219</v>
       </c>
@@ -3910,7 +3960,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
+      <c r="A12" s="27"/>
       <c r="C12" t="s">
         <v>220</v>
       </c>
@@ -3925,7 +3975,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="27" t="s">
         <v>221</v>
       </c>
       <c r="C13" t="s">
@@ -3942,7 +3992,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
+      <c r="A14" s="27"/>
       <c r="C14" t="s">
         <v>231</v>
       </c>
@@ -3957,7 +4007,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
+      <c r="A15" s="27"/>
       <c r="C15" t="s">
         <v>232</v>
       </c>
@@ -3972,7 +4022,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
+      <c r="A16" s="27"/>
       <c r="C16" t="s">
         <v>233</v>
       </c>
@@ -3987,156 +4037,156 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="27" t="s">
         <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
+      <c r="A18" s="27"/>
       <c r="C18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F18" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
+      <c r="A19" s="27"/>
       <c r="C19" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="F19" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A20" s="29" t="s">
-        <v>283</v>
+      <c r="A20" s="28" t="s">
+        <v>281</v>
       </c>
       <c r="C20" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A21" s="28"/>
+      <c r="C21" t="s">
         <v>297</v>
-      </c>
-      <c r="F20" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A21" s="29"/>
-      <c r="C21" t="s">
-        <v>299</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F21" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A22" s="29"/>
+      <c r="A22" s="28"/>
       <c r="C22" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="F22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A23" s="29"/>
+      <c r="A23" s="28"/>
       <c r="C23" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F23" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A24" s="29"/>
+      <c r="A24" s="28"/>
       <c r="C24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="F24" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A25" s="29"/>
+      <c r="A25" s="28"/>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F25" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F26" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -4187,420 +4237,420 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="56" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
-        <v>308</v>
+      <c r="A2" s="27" t="s">
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="F2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="27"/>
       <c r="B3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="27"/>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="F4" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="27"/>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="F5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="27"/>
       <c r="B6" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="27"/>
       <c r="B7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="F7" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>321</v>
+      <c r="A8" s="27" t="s">
+        <v>318</v>
       </c>
       <c r="B8" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F8" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
+      <c r="A9" s="27"/>
       <c r="B9" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="27"/>
       <c r="B10" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F10" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
+      <c r="A11" s="27"/>
       <c r="B11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="56" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>330</v>
+      <c r="A12" s="27" t="s">
+        <v>327</v>
       </c>
       <c r="B12" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F12" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
+      <c r="A13" s="27"/>
       <c r="B13" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F13" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
+      <c r="A14" s="27"/>
       <c r="B14" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F14" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
+      <c r="A15" s="27"/>
       <c r="B15" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="F15" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="s">
-        <v>339</v>
+      <c r="A16" s="27" t="s">
+        <v>336</v>
       </c>
       <c r="B16" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="F16" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
+      <c r="A17" s="27"/>
       <c r="B17" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F17" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
+      <c r="A18" s="27"/>
       <c r="B18" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="F18" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="31"/>
+      <c r="A19" s="27"/>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="F19" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
+      <c r="A20" s="27"/>
       <c r="B20" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F20" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
-        <v>350</v>
+      <c r="A21" s="27" t="s">
+        <v>347</v>
       </c>
       <c r="B21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="F21" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
+      <c r="A22" s="27"/>
       <c r="B22" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F22" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A23" s="31"/>
+      <c r="A23" s="27"/>
       <c r="B23" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F23" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
+      <c r="A24" s="27"/>
       <c r="B24" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F24" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="168" x14ac:dyDescent="0.3">
-      <c r="A25" s="31" t="s">
-        <v>359</v>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="84" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>356</v>
       </c>
       <c r="B25" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="F25" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="56" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
+        <v>358</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
       <c r="B26" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F26" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="56" x14ac:dyDescent="0.3">
-      <c r="A27" s="31"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
       <c r="B27" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="F27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="98" x14ac:dyDescent="0.3">
-      <c r="A28" s="31"/>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A28" s="27"/>
       <c r="B28" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F28" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -4653,24 +4703,24 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="27" t="s">
         <v>243</v>
       </c>
       <c r="C2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="27"/>
       <c r="C3" t="s">
         <v>244</v>
       </c>
@@ -4678,14 +4728,14 @@
         <v>5</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F3" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="27"/>
       <c r="C4" t="s">
         <v>245</v>
       </c>
@@ -4693,14 +4743,14 @@
         <v>3</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="27"/>
       <c r="C5" t="s">
         <v>246</v>
       </c>
@@ -4708,399 +4758,399 @@
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="F5" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
-      <c r="C6" t="s">
-        <v>247</v>
+      <c r="A6" s="27"/>
+      <c r="C6" s="32" t="s">
+        <v>453</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="27"/>
       <c r="C7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D7">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
+      <c r="A8" s="27"/>
       <c r="C8" t="s">
-        <v>249</v>
+        <v>452</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="F8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
+      <c r="A9" s="27"/>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D9">
         <v>5</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="F9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="27"/>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D10">
         <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F10" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>250</v>
+      <c r="A11" s="27" t="s">
+        <v>248</v>
       </c>
       <c r="C11" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="F11" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
+      <c r="A12" s="27"/>
       <c r="C12" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="F12" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
+      <c r="A13" s="27"/>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D13">
         <v>5</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="F13" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
+      <c r="A14" s="27"/>
       <c r="C14" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F14" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
+      <c r="A15" s="27"/>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F15" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
+      <c r="A16" s="27"/>
       <c r="C16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D16">
         <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="F16" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
+      <c r="A17" s="27"/>
       <c r="C17" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D17">
         <v>5</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="F17" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="31"/>
+      <c r="A18" s="27"/>
       <c r="C18" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F18" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A19" s="31" t="s">
-        <v>259</v>
+      <c r="A19" s="27" t="s">
+        <v>257</v>
       </c>
       <c r="C19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="F19" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A20" s="31"/>
+      <c r="A20" s="27"/>
       <c r="C20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F20" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A21" s="31"/>
+      <c r="A21" s="27"/>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F21" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A22" s="31"/>
+      <c r="A22" s="27"/>
       <c r="C22" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F22" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
-        <v>264</v>
+      <c r="A23" s="27" t="s">
+        <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D23">
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="F23" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="56" x14ac:dyDescent="0.3">
-      <c r="A24" s="31"/>
+      <c r="A24" s="27"/>
       <c r="C24" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F24" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A25" s="31"/>
+      <c r="A25" s="27"/>
       <c r="C25" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D25">
         <v>3</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="F25" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
+      <c r="A26" s="27"/>
       <c r="C26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F26" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A27" s="31"/>
+      <c r="A27" s="27"/>
       <c r="C27" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F27" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A28" s="31" t="s">
-        <v>270</v>
+      <c r="A28" s="27" t="s">
+        <v>268</v>
       </c>
       <c r="C28" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D28">
         <v>3</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F28" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A29" s="31"/>
+      <c r="A29" s="27"/>
       <c r="C29" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D29">
         <v>4</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="F29" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A30" s="31"/>
+      <c r="A30" s="27"/>
       <c r="C30" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D30">
         <v>3</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F30" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="31"/>
+      <c r="A31" s="27"/>
       <c r="C31" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Subject\PBLsax\-SchoolActPlatform\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4685AEAB-3BA2-4F72-AD56-88BEADB0B380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D543685-2E10-4B54-AD95-D227DD4101DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="5" xr2:uid="{1ACCA5E6-2984-4267-850E-A4BD19BC86B6}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="活动管理核心功能" sheetId="3" r:id="rId3"/>
     <sheet name="活动报名与收藏" sheetId="4" r:id="rId4"/>
     <sheet name="评论互动与系统优化" sheetId="5" r:id="rId5"/>
-    <sheet name="资源搜索" sheetId="8" r:id="rId6"/>
+    <sheet name="活动搜索" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="403">
   <si>
     <t>分数</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1107,99 +1107,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>关键词搜索</t>
-  </si>
-  <si>
-    <t>模糊关键词搜索</t>
-  </si>
-  <si>
-    <t>空关键词搜索</t>
-  </si>
-  <si>
-    <t>特殊字符搜索</t>
-  </si>
-  <si>
-    <t>搜索词前后空格处理</t>
-  </si>
-  <si>
-    <t>按资源类型筛选</t>
-  </si>
-  <si>
-    <t>选择单一类型-视频</t>
-  </si>
-  <si>
-    <t>选择单一类型-文档</t>
-  </si>
-  <si>
-    <t>选择单一类型-音频</t>
-  </si>
-  <si>
-    <t>不选择类型（全部）</t>
-  </si>
-  <si>
-    <t>选择"初级"</t>
-  </si>
-  <si>
-    <t>选择"中级"</t>
-  </si>
-  <si>
-    <t>选择"高级"</t>
-  </si>
-  <si>
-    <t>不选择难度（全部）</t>
-  </si>
-  <si>
-    <t>按标签筛选</t>
-  </si>
-  <si>
-    <t>选择单个标签</t>
-  </si>
-  <si>
-    <t>选择多个标签(并集/交集)</t>
-  </si>
-  <si>
-    <t>取消已选标签</t>
-  </si>
-  <si>
-    <t>不选择标签（全部）</t>
-  </si>
-  <si>
-    <t>组合搜索</t>
-  </si>
-  <si>
-    <t>关键词+资源类型</t>
-  </si>
-  <si>
-    <t>关键词+难度级别</t>
-  </si>
-  <si>
-    <t>关键词+标签</t>
-  </si>
-  <si>
-    <t>类型+难度+标签（全组合）</t>
-  </si>
-  <si>
-    <t>搜索+全筛选条件无结果</t>
-  </si>
-  <si>
-    <t>搜索结果展示</t>
-  </si>
-  <si>
-    <t>搜索结果数量显示</t>
-  </si>
-  <si>
-    <t>搜索结果分页</t>
-  </si>
-  <si>
-    <t>搜索结果排序</t>
-  </si>
-  <si>
-    <t>搜索结果中资源详情入口</t>
-  </si>
-  <si>
-    <t>点击重置按钮</t>
-  </si>
-  <si>
     <t>正常收藏活动</t>
   </si>
   <si>
@@ -1219,10 +1126,6 @@
   </si>
   <si>
     <t>收藏活动已删除处理</t>
-  </si>
-  <si>
-    <t>收藏功能</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>提示"收藏成功"，图标变为已收藏状态</t>
@@ -1656,319 +1559,221 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>返回标题或描述包含"Python入门教程"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回所有包含"Python"的资源（如Python入门、Python进阶等）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示全部资源或提示"请输入搜索关键词"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>系统正常处理，提示"未找到相关资源"或返回匹配结果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示"未找到相关资源"或空结果页，给出搜索建议</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动去除首尾空格，正常搜索"Python"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>能搜索到标题含"Python"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示类型为"视频"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示类型为"文档"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示类型为"音频"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回所有类型的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示难度为"初级"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示难度为"中级"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示难度为"高级"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回所有难度的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>只显示包含"机器学习"标签的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>根据系统逻辑：显示同时满足或任一满足的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>搜索结果不再受该标签限制</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回所有标签的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回类型为"视频"且包含"Python"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回难度为"初级"且包含"机器学习"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回含"Python"标签且匹配"数据分析"的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>返回同时满足三个条件的资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示"未找到相关资源"，建议放宽条件</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示"共找到X个资源"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>正常加载后续结果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>列表按所选排序正确排列</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>跳转到资源详情页</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>所有条件清空，恢复默认显示全部资源</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>重置搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>精确关键词搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 设置多个搜索条件
-2. 点击"重置"</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 在搜索结果列表
-2. 点击某资源标题</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 执行搜索
-2. 切换排序方式（按时间/相关度/热度）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 搜索结果超过单页数量
-2. 点击下一页或滚动</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 执行搜索
-2. 查看页面顶部或底部</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入关键词+多个筛选条件
-2. 条件组合无匹配结果</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择类型"视频"
-2. 选择难度"中级"
-3. 选择标签"深度学习"
-4. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入"数据分析"
-2. 选择标签"Python"
-3. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入"机器学习"
-2. 选择难度"初级"
-3. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入"Python"
-2. 选择类型"视频"
-3. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 标签不选
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 已选"机器学习"
-2. 再次点击取消选择
-3. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 同时勾选"机器学习"和"Python"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择标签"机器学习"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 难度级别选择"全部"或不选
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择难度"高级"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择难度"中级"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择难度级别"初级"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 资源类型选择"全部"或不选
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择类型"音频"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 选择类型"文档"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 在筛选条件中选择类型"视频"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入"python"（全小写）
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入" Python "（前后有空格）
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入不存在的关键词"xyz123不存在"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入"@#$%"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 关键词留空
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 输入关键词"Python"
-2. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. 进入资源搜索页面
-2. 输入完整关键词"Python入门教程"
-3. 点击搜索</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>大小写不敏感</t>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>列表中只显示标题完全匹配的活动</t>
+  </si>
+  <si>
+    <t>显示标题或描述中包含“歌手”的活动</t>
+  </si>
+  <si>
+    <t>活动搜索_关键词_大小写不敏感</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>输入“Campus”</t>
+  </si>
+  <si>
+    <t>与输入“campus”结果一致</t>
+  </si>
+  <si>
+    <t>活动搜索_关键词_前后空格</t>
+  </si>
+  <si>
+    <t>输入“ 歌手 ”</t>
+  </si>
+  <si>
+    <t>自动 trim，按“歌手”搜索</t>
+  </si>
+  <si>
+    <t>活动搜索_关键词_无结果</t>
+  </si>
+  <si>
+    <t>输入“不存在活动xyz”</t>
+  </si>
+  <si>
+    <t>显示“未找到相关活动”+ 推荐其他活动</t>
+  </si>
+  <si>
+    <t>活动搜索_筛选_按活动类型</t>
+  </si>
+  <si>
+    <t>选择类型“讲座”</t>
+  </si>
+  <si>
+    <t>只显示类型为“讲座”的活动</t>
+  </si>
+  <si>
+    <t>活动搜索_筛选_按活动状态</t>
+  </si>
+  <si>
+    <t>选择状态“报名中”</t>
+  </si>
+  <si>
+    <t>只显示报名开始后、结束前的活动</t>
+  </si>
+  <si>
+    <t>活动搜索_筛选_按时间范围</t>
+  </si>
+  <si>
+    <t>选择“本周”</t>
+  </si>
+  <si>
+    <t>只显示开始时间在本周内的活动</t>
+  </si>
+  <si>
+    <t>活动搜索_组合_关键词+类型</t>
+  </si>
+  <si>
+    <t>输入“Python”+ 类型“讲座”</t>
+  </si>
+  <si>
+    <t>显示标题/描述含Python且类型为讲座的活动</t>
+  </si>
+  <si>
+    <t>活动搜索_组合_关键词+状态+类型</t>
+  </si>
+  <si>
+    <t>输入“比赛”+ 状态“报名中”+ 类型“比赛”</t>
+  </si>
+  <si>
+    <t>同时满足三者</t>
+  </si>
+  <si>
+    <t>活动搜索_重置_清空所有条件</t>
+  </si>
+  <si>
+    <t>填写多个条件后点击“重置”</t>
+  </si>
+  <si>
+    <t>关键词清空，筛选恢复默认，显示全部活动</t>
+  </si>
+  <si>
+    <t>活动搜索_结果展示_分页</t>
+  </si>
+  <si>
+    <t>搜索后结果超过10条</t>
+  </si>
+  <si>
+    <t>显示分页组件，点击下一页正常加载</t>
+  </si>
+  <si>
+    <t>活动搜索_结果展示_排序</t>
+  </si>
+  <si>
+    <t>按“开始时间升序”</t>
+  </si>
+  <si>
+    <t>列表按时间从近到远排列</t>
+  </si>
+  <si>
+    <t>活动搜索</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="6"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>活动搜索</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关键词</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精确匹配</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>输入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>无匹配结果(</t>
+      <t>歌手</t>
     </r>
     <r>
       <rPr>
-        <sz val="6"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
       </rPr>
-      <t>无法一眼知其含义，不符合所给出的用例规范</t>
+      <t>”</t>
     </r>
-    <r>
-      <rPr>
-        <sz val="6"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
+  </si>
+  <si>
+    <t>1. 进入活动列表页
+2. 输入完整活动标题“校园歌手大赛”
+3. 点击搜索</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动搜索_关键词_模糊匹配</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>活动收藏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2083,23 +1888,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="等线"/>
-      <family val="3"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2118,6 +1922,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2128,8 +1937,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2215,7 +2027,13 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -2224,18 +2042,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="着色 1" xfId="1" builtinId="29"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2567,10 +2380,10 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="29">
+      <c r="B2" s="31">
         <v>25</v>
       </c>
       <c r="C2" t="s">
@@ -2578,22 +2391,22 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="31"/>
       <c r="C3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="29"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="31"/>
       <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="29">
+      <c r="A5" s="30"/>
+      <c r="B5" s="31">
         <v>18</v>
       </c>
       <c r="C5" t="s">
@@ -2601,16 +2414,16 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="31"/>
     </row>
     <row r="7" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="29"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="31"/>
     </row>
     <row r="8" spans="1:3" ht="24.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29">
+      <c r="A8" s="30"/>
+      <c r="B8" s="31">
         <v>21</v>
       </c>
       <c r="C8" t="s">
@@ -2619,14 +2432,14 @@
     </row>
     <row r="9" spans="1:3" ht="2" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
-      <c r="B9" s="29"/>
+      <c r="B9" s="31"/>
     </row>
     <row r="10" spans="1:3" ht="16.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="29"/>
+      <c r="B10" s="31"/>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="30" t="s">
         <v>31</v>
       </c>
       <c r="B11" s="2">
@@ -2637,8 +2450,8 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="29">
+      <c r="A12" s="30"/>
+      <c r="B12" s="31">
         <v>16</v>
       </c>
       <c r="C12" t="s">
@@ -2646,21 +2459,21 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="31"/>
       <c r="C13" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="30"/>
+      <c r="B14" s="31"/>
       <c r="C14" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="30" t="s">
         <v>32</v>
       </c>
       <c r="B15" s="2">
@@ -2671,42 +2484,42 @@
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
+      <c r="A16" s="30"/>
       <c r="B16" s="12"/>
       <c r="C16" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="12"/>
       <c r="C17" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
+      <c r="A18" s="30"/>
       <c r="B18" s="12"/>
       <c r="C18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="13"/>
       <c r="C19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
+      <c r="A20" s="30"/>
       <c r="B20" s="13"/>
       <c r="C20" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="30" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="13"/>
@@ -2715,28 +2528,28 @@
       </c>
     </row>
     <row r="22" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+      <c r="A22" s="30"/>
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="30"/>
       <c r="B23" s="13"/>
       <c r="C23" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="30"/>
       <c r="B24" s="13"/>
       <c r="C24" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="30"/>
       <c r="B25" s="13"/>
       <c r="C25" t="s">
         <v>29</v>
@@ -2795,7 +2608,7 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="28" t="s">
         <v>34</v>
       </c>
       <c r="B2" s="15"/>
@@ -2813,7 +2626,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="30"/>
+      <c r="A3" s="28"/>
       <c r="B3" s="18"/>
       <c r="C3" s="16" t="s">
         <v>36</v>
@@ -2829,7 +2642,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="31" t="s">
+      <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="18"/>
@@ -2847,7 +2660,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="18"/>
       <c r="C5" s="20" t="s">
         <v>38</v>
@@ -2863,7 +2676,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="18"/>
       <c r="C6" s="15" t="s">
         <v>39</v>
@@ -2879,7 +2692,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="18"/>
       <c r="C7" s="15" t="s">
         <v>40</v>
@@ -2895,7 +2708,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A8" s="31"/>
+      <c r="A8" s="29"/>
       <c r="B8" s="18"/>
       <c r="C8" s="15" t="s">
         <v>41</v>
@@ -2911,7 +2724,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A9" s="31"/>
+      <c r="A9" s="29"/>
       <c r="B9" s="15"/>
       <c r="C9" s="15" t="s">
         <v>42</v>
@@ -2927,7 +2740,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
+      <c r="A10" s="29"/>
       <c r="B10" s="15"/>
       <c r="C10" s="15" t="s">
         <v>43</v>
@@ -2943,7 +2756,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A11" s="31"/>
+      <c r="A11" s="29"/>
       <c r="B11" s="18"/>
       <c r="C11" s="15" t="s">
         <v>44</v>
@@ -2959,7 +2772,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="28" t="s">
         <v>62</v>
       </c>
       <c r="B12" s="15"/>
@@ -2977,7 +2790,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="30"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="18"/>
       <c r="C13" s="16" t="s">
         <v>60</v>
@@ -2993,7 +2806,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="18"/>
       <c r="C14" s="15" t="s">
         <v>45</v>
@@ -3009,7 +2822,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
+      <c r="A15" s="28"/>
       <c r="B15" s="18"/>
       <c r="C15" s="15" t="s">
         <v>46</v>
@@ -3025,7 +2838,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="18"/>
       <c r="C16" s="15" t="s">
         <v>47</v>
@@ -3041,7 +2854,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="30"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="18"/>
       <c r="C17" s="16" t="s">
         <v>48</v>
@@ -3057,7 +2870,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="30" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="18"/>
@@ -3075,7 +2888,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="18"/>
       <c r="C19" s="15" t="s">
         <v>51</v>
@@ -3091,7 +2904,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="62" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="18"/>
       <c r="C20" s="15" t="s">
         <v>52</v>
@@ -3107,7 +2920,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="30"/>
+      <c r="A21" s="28"/>
       <c r="B21" s="18"/>
       <c r="C21" s="15" t="s">
         <v>53</v>
@@ -3123,7 +2936,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="28" t="s">
         <v>55</v>
       </c>
       <c r="B22" s="18"/>
@@ -3141,7 +2954,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
+      <c r="A23" s="28"/>
       <c r="B23" s="18"/>
       <c r="C23" s="16" t="s">
         <v>56</v>
@@ -3157,7 +2970,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="30"/>
+      <c r="A24" s="28"/>
       <c r="B24" s="18"/>
       <c r="C24" s="16" t="s">
         <v>57</v>
@@ -3173,7 +2986,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
+      <c r="A25" s="28"/>
       <c r="B25" s="18"/>
       <c r="C25" s="15" t="s">
         <v>58</v>
@@ -3254,7 +3067,7 @@
       <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="77.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="29" t="s">
         <v>69</v>
       </c>
       <c r="B2" s="18"/>
@@ -3274,7 +3087,7 @@
       <c r="H2" s="24"/>
     </row>
     <row r="3" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="31"/>
+      <c r="A3" s="29"/>
       <c r="B3" s="18"/>
       <c r="C3" s="16" t="s">
         <v>71</v>
@@ -3292,7 +3105,7 @@
       <c r="H3" s="24"/>
     </row>
     <row r="4" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A4" s="31"/>
+      <c r="A4" s="29"/>
       <c r="B4" s="18"/>
       <c r="C4" s="16" t="s">
         <v>72</v>
@@ -3310,7 +3123,7 @@
       <c r="H4" s="24"/>
     </row>
     <row r="5" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+      <c r="A5" s="29"/>
       <c r="B5" s="18"/>
       <c r="C5" s="16" t="s">
         <v>73</v>
@@ -3328,7 +3141,7 @@
       <c r="H5" s="24"/>
     </row>
     <row r="6" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A6" s="31"/>
+      <c r="A6" s="29"/>
       <c r="B6" s="18"/>
       <c r="C6" s="16" t="s">
         <v>74</v>
@@ -3346,7 +3159,7 @@
       <c r="H6" s="24"/>
     </row>
     <row r="7" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A7" s="31"/>
+      <c r="A7" s="29"/>
       <c r="B7" s="18"/>
       <c r="C7" s="16" t="s">
         <v>75</v>
@@ -3364,7 +3177,7 @@
       <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" ht="62" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="28" t="s">
         <v>76</v>
       </c>
       <c r="B8" s="18"/>
@@ -3384,7 +3197,7 @@
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="30"/>
+      <c r="A9" s="28"/>
       <c r="B9" s="18"/>
       <c r="C9" s="20" t="s">
         <v>78</v>
@@ -3402,7 +3215,7 @@
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
+      <c r="A10" s="28"/>
       <c r="B10" s="18"/>
       <c r="C10" s="16" t="s">
         <v>79</v>
@@ -3420,7 +3233,7 @@
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" ht="46.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="28" t="s">
         <v>80</v>
       </c>
       <c r="B11" s="18"/>
@@ -3440,7 +3253,7 @@
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A12" s="30"/>
+      <c r="A12" s="28"/>
       <c r="B12" s="18"/>
       <c r="C12" s="16" t="s">
         <v>82</v>
@@ -3458,7 +3271,7 @@
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A13" s="30"/>
+      <c r="A13" s="28"/>
       <c r="B13" s="18"/>
       <c r="C13" s="16" t="s">
         <v>83</v>
@@ -3476,7 +3289,7 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
+      <c r="A14" s="28"/>
       <c r="B14" s="18"/>
       <c r="C14" s="16" t="s">
         <v>84</v>
@@ -3494,7 +3307,7 @@
       <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="28" t="s">
         <v>85</v>
       </c>
       <c r="B15" s="18"/>
@@ -3514,7 +3327,7 @@
       <c r="H15" s="24"/>
     </row>
     <row r="16" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
+      <c r="A16" s="28"/>
       <c r="B16" s="18"/>
       <c r="C16" s="16" t="s">
         <v>87</v>
@@ -3532,7 +3345,7 @@
       <c r="H16" s="24"/>
     </row>
     <row r="17" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A17" s="30"/>
+      <c r="A17" s="28"/>
       <c r="B17" s="18"/>
       <c r="C17" s="16" t="s">
         <v>88</v>
@@ -3550,7 +3363,7 @@
       <c r="H17" s="24"/>
     </row>
     <row r="18" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A18" s="30"/>
+      <c r="A18" s="28"/>
       <c r="B18" s="18"/>
       <c r="C18" s="16" t="s">
         <v>89</v>
@@ -3568,7 +3381,7 @@
       <c r="H18" s="24"/>
     </row>
     <row r="19" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
+      <c r="A19" s="28"/>
       <c r="B19" s="18"/>
       <c r="C19" s="16" t="s">
         <v>90</v>
@@ -3586,7 +3399,7 @@
       <c r="H19" s="24"/>
     </row>
     <row r="20" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
+      <c r="A20" s="28"/>
       <c r="B20" s="18"/>
       <c r="C20" s="16" t="s">
         <v>91</v>
@@ -3604,7 +3417,7 @@
       <c r="H20" s="24"/>
     </row>
     <row r="21" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="28" t="s">
         <v>92</v>
       </c>
       <c r="B21" s="18"/>
@@ -3624,7 +3437,7 @@
       <c r="H21" s="24"/>
     </row>
     <row r="22" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
+      <c r="A22" s="28"/>
       <c r="B22" s="18"/>
       <c r="C22" s="16" t="s">
         <v>94</v>
@@ -3642,7 +3455,7 @@
       <c r="H22" s="24"/>
     </row>
     <row r="23" spans="1:8" ht="15.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
+      <c r="A23" s="28"/>
       <c r="B23" s="18"/>
       <c r="C23" s="16" t="s">
         <v>95</v>
@@ -3660,7 +3473,7 @@
       <c r="H23" s="24"/>
     </row>
     <row r="24" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="28" t="s">
         <v>96</v>
       </c>
       <c r="B24" s="18"/>
@@ -3680,7 +3493,7 @@
       <c r="H24" s="24"/>
     </row>
     <row r="25" spans="1:8" ht="31" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
+      <c r="A25" s="28"/>
       <c r="B25" s="18"/>
       <c r="C25" s="16" t="s">
         <v>98</v>
@@ -3806,7 +3619,7 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="32" t="s">
         <v>194</v>
       </c>
       <c r="C2" t="s">
@@ -3823,7 +3636,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
+      <c r="A3" s="32"/>
       <c r="C3" t="s">
         <v>196</v>
       </c>
@@ -3838,7 +3651,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
+      <c r="A4" s="32"/>
       <c r="C4" t="s">
         <v>197</v>
       </c>
@@ -3853,7 +3666,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
+      <c r="A5" s="32"/>
       <c r="C5" t="s">
         <v>198</v>
       </c>
@@ -3868,7 +3681,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
+      <c r="A6" s="32"/>
       <c r="C6" t="s">
         <v>199</v>
       </c>
@@ -3883,7 +3696,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
+      <c r="A7" s="32"/>
       <c r="C7" t="s">
         <v>200</v>
       </c>
@@ -3898,7 +3711,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
+      <c r="A8" s="32"/>
       <c r="C8" t="s">
         <v>201</v>
       </c>
@@ -3913,7 +3726,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="32" t="s">
         <v>216</v>
       </c>
       <c r="C9" t="s">
@@ -3930,7 +3743,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+      <c r="A10" s="32"/>
       <c r="C10" t="s">
         <v>218</v>
       </c>
@@ -3945,7 +3758,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
+      <c r="A11" s="32"/>
       <c r="C11" t="s">
         <v>219</v>
       </c>
@@ -3960,7 +3773,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
+      <c r="A12" s="32"/>
       <c r="C12" t="s">
         <v>220</v>
       </c>
@@ -3975,7 +3788,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="32" t="s">
         <v>221</v>
       </c>
       <c r="C13" t="s">
@@ -3992,7 +3805,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+      <c r="A14" s="32"/>
       <c r="C14" t="s">
         <v>231</v>
       </c>
@@ -4007,7 +3820,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
+      <c r="A15" s="32"/>
       <c r="C15" t="s">
         <v>232</v>
       </c>
@@ -4022,7 +3835,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
+      <c r="A16" s="32"/>
       <c r="C16" t="s">
         <v>233</v>
       </c>
@@ -4037,156 +3850,157 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="32" t="s">
         <v>242</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>257</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>292</v>
+        <v>260</v>
       </c>
       <c r="F17" t="s">
-        <v>305</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
+      <c r="A18" s="32"/>
       <c r="C18" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="D18">
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>293</v>
+        <v>261</v>
       </c>
       <c r="F18" t="s">
-        <v>304</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
+      <c r="A19" s="32"/>
       <c r="C19" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="F19" t="s">
-        <v>303</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A20" s="28" t="s">
-        <v>281</v>
+      <c r="A20" s="32" t="s">
+        <v>402</v>
       </c>
       <c r="C20" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="F20" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
+      <c r="A21" s="32"/>
       <c r="C21" t="s">
-        <v>297</v>
+        <v>265</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="F21" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
+      <c r="A22" s="32"/>
       <c r="C22" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="D22">
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>298</v>
+        <v>266</v>
       </c>
       <c r="F22" t="s">
-        <v>284</v>
+        <v>252</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
+      <c r="A23" s="32"/>
       <c r="C23" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="F23" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
+      <c r="A24" s="32"/>
       <c r="C24" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="D24">
         <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="F24" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
+      <c r="A25" s="32"/>
       <c r="C25" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="D25">
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="F25" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
+      <c r="A26" s="32"/>
       <c r="C26" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>302</v>
+        <v>270</v>
       </c>
       <c r="F26" t="s">
-        <v>288</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -4194,8 +4008,8 @@
     <mergeCell ref="A2:A8"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A20:A25"/>
     <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A20:A26"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4237,420 +4051,420 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="1:8" ht="56" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>306</v>
+      <c r="A2" s="32" t="s">
+        <v>274</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>275</v>
       </c>
       <c r="D2">
         <v>5</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>391</v>
+        <v>359</v>
       </c>
       <c r="F2" t="s">
-        <v>308</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
+      <c r="A3" s="32"/>
       <c r="B3" t="s">
-        <v>309</v>
+        <v>277</v>
       </c>
       <c r="D3">
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>390</v>
+        <v>358</v>
       </c>
       <c r="F3" t="s">
-        <v>310</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
+      <c r="A4" s="32"/>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>279</v>
       </c>
       <c r="D4">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>389</v>
+        <v>357</v>
       </c>
       <c r="F4" t="s">
-        <v>312</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
+      <c r="A5" s="32"/>
       <c r="B5" t="s">
-        <v>313</v>
+        <v>281</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>388</v>
+        <v>356</v>
       </c>
       <c r="F5" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
+      <c r="A6" s="32"/>
       <c r="B6" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="D6">
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>387</v>
+        <v>355</v>
       </c>
       <c r="F6" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
+      <c r="A7" s="32"/>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="D7">
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>386</v>
+        <v>354</v>
       </c>
       <c r="F7" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
-        <v>318</v>
+      <c r="A8" s="32" t="s">
+        <v>286</v>
       </c>
       <c r="B8" t="s">
-        <v>319</v>
+        <v>287</v>
       </c>
       <c r="D8">
         <v>5</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="F8" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
+      <c r="A9" s="32"/>
       <c r="B9" t="s">
-        <v>321</v>
+        <v>289</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>384</v>
+        <v>352</v>
       </c>
       <c r="F9" t="s">
-        <v>322</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
+      <c r="A10" s="32"/>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>291</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>383</v>
+        <v>351</v>
       </c>
       <c r="F10" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="27"/>
+      <c r="A11" s="32"/>
       <c r="B11" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>382</v>
+        <v>350</v>
       </c>
       <c r="F11" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="56" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
-        <v>327</v>
+      <c r="A12" s="32" t="s">
+        <v>295</v>
       </c>
       <c r="B12" t="s">
-        <v>328</v>
+        <v>296</v>
       </c>
       <c r="D12">
         <v>5</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>381</v>
+        <v>349</v>
       </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
+      <c r="A13" s="32"/>
       <c r="B13" t="s">
-        <v>330</v>
+        <v>298</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
+      <c r="A14" s="32"/>
       <c r="B14" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="F14" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
+      <c r="A15" s="32"/>
       <c r="B15" t="s">
-        <v>334</v>
+        <v>302</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>378</v>
+        <v>346</v>
       </c>
       <c r="F15" t="s">
-        <v>335</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
-        <v>336</v>
+      <c r="A16" s="32" t="s">
+        <v>304</v>
       </c>
       <c r="B16" t="s">
-        <v>337</v>
+        <v>305</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>377</v>
+        <v>345</v>
       </c>
       <c r="F16" t="s">
-        <v>338</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
+      <c r="A17" s="32"/>
       <c r="B17" t="s">
-        <v>339</v>
+        <v>307</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>376</v>
+        <v>344</v>
       </c>
       <c r="F17" t="s">
-        <v>340</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
+      <c r="A18" s="32"/>
       <c r="B18" t="s">
-        <v>341</v>
+        <v>309</v>
       </c>
       <c r="D18">
         <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>375</v>
+        <v>343</v>
       </c>
       <c r="F18" t="s">
-        <v>342</v>
+        <v>310</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A19" s="27"/>
+      <c r="A19" s="32"/>
       <c r="B19" t="s">
-        <v>343</v>
+        <v>311</v>
       </c>
       <c r="D19">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>374</v>
+        <v>342</v>
       </c>
       <c r="F19" t="s">
-        <v>344</v>
+        <v>312</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
+      <c r="A20" s="32"/>
       <c r="B20" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="D20">
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>373</v>
+        <v>341</v>
       </c>
       <c r="F20" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A21" s="27" t="s">
-        <v>347</v>
+      <c r="A21" s="32" t="s">
+        <v>315</v>
       </c>
       <c r="B21" t="s">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="D21">
         <v>3</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>372</v>
+        <v>340</v>
       </c>
       <c r="F21" t="s">
-        <v>349</v>
+        <v>317</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
+      <c r="A22" s="32"/>
       <c r="B22" t="s">
-        <v>350</v>
+        <v>318</v>
       </c>
       <c r="D22">
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="F22" t="s">
-        <v>351</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A23" s="27"/>
+      <c r="A23" s="32"/>
       <c r="B23" t="s">
-        <v>352</v>
+        <v>320</v>
       </c>
       <c r="D23">
         <v>3</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>370</v>
+        <v>338</v>
       </c>
       <c r="F23" t="s">
-        <v>353</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
+      <c r="A24" s="32"/>
       <c r="B24" t="s">
-        <v>354</v>
+        <v>322</v>
       </c>
       <c r="D24">
         <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>369</v>
+        <v>337</v>
       </c>
       <c r="F24" t="s">
-        <v>355</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="84" x14ac:dyDescent="0.3">
-      <c r="A25" s="27" t="s">
-        <v>356</v>
+      <c r="A25" s="32" t="s">
+        <v>324</v>
       </c>
       <c r="B25" t="s">
-        <v>357</v>
+        <v>325</v>
       </c>
       <c r="D25">
         <v>5</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>368</v>
+        <v>336</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>326</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
+      <c r="A26" s="32"/>
       <c r="B26" t="s">
-        <v>359</v>
+        <v>327</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>367</v>
+        <v>335</v>
       </c>
       <c r="F26" t="s">
-        <v>360</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
+      <c r="A27" s="32"/>
       <c r="B27" t="s">
-        <v>361</v>
+        <v>329</v>
       </c>
       <c r="D27">
         <v>3</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="F27" t="s">
-        <v>362</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
+      <c r="A28" s="32"/>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>331</v>
       </c>
       <c r="D28">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>365</v>
+        <v>333</v>
       </c>
       <c r="F28" t="s">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -4669,7 +4483,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F28461A-81FC-4C45-97A2-B9AEB4AC09F4}">
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.4140625" customWidth="1"/>
@@ -4680,486 +4494,245 @@
     <col min="6" max="6" width="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="D1" s="27" t="s">
         <v>66</v>
       </c>
+      <c r="E1" s="27" t="s">
+        <v>67</v>
+      </c>
       <c r="F1" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="42" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="C2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>451</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="30" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="E2" s="30" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="30"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+    </row>
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="30"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="30"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+    </row>
+    <row r="5" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" t="s">
+        <v>401</v>
+      </c>
+      <c r="C5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D5" t="s">
+        <v>399</v>
+      </c>
+      <c r="E5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="30"/>
+      <c r="B6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E6" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="30"/>
+      <c r="B7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E7" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="30"/>
+      <c r="B8" t="s">
+        <v>370</v>
+      </c>
+      <c r="C8" t="s">
+        <v>364</v>
+      </c>
+      <c r="D8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D9" t="s">
+        <v>374</v>
+      </c>
+      <c r="E9" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
+      <c r="B10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" t="s">
+        <v>360</v>
+      </c>
+      <c r="D10" t="s">
+        <v>377</v>
+      </c>
+      <c r="E10" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="30"/>
+      <c r="B11" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" t="s">
+        <v>364</v>
+      </c>
+      <c r="D11" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="30"/>
+      <c r="B12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C12" t="s">
+        <v>360</v>
+      </c>
+      <c r="D12" t="s">
+        <v>383</v>
+      </c>
+      <c r="E12" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="30"/>
+      <c r="B13" t="s">
+        <v>385</v>
+      </c>
+      <c r="C13" t="s">
+        <v>364</v>
+      </c>
+      <c r="D13" t="s">
+        <v>386</v>
+      </c>
+      <c r="E13" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="30"/>
+      <c r="B14" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="30"/>
+      <c r="B15" t="s">
+        <v>391</v>
+      </c>
+      <c r="C15" t="s">
+        <v>364</v>
+      </c>
+      <c r="D15" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A3" s="27"/>
-      <c r="C3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E15" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A4" s="27"/>
-      <c r="C4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="30"/>
+      <c r="B16" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A5" s="27"/>
-      <c r="C5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>448</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="C16" t="s">
+        <v>364</v>
+      </c>
+      <c r="D16" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A6" s="27"/>
-      <c r="C6" s="32" t="s">
-        <v>453</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>447</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E16" t="s">
         <v>396</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A7" s="27"/>
-      <c r="C7" t="s">
-        <v>247</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="F7" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="C8" t="s">
-        <v>452</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="F8" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="C9" t="s">
-        <v>249</v>
-      </c>
-      <c r="D9">
-        <v>5</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="F9" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="C10" t="s">
-        <v>250</v>
-      </c>
-      <c r="D10">
-        <v>4</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F10" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="C11" t="s">
-        <v>251</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>442</v>
-      </c>
-      <c r="F11" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A12" s="27"/>
-      <c r="C12" t="s">
-        <v>252</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="F12" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A13" s="27"/>
-      <c r="C13" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="F13" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A14" s="27"/>
-      <c r="C14" t="s">
-        <v>254</v>
-      </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="F14" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A15" s="27"/>
-      <c r="C15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D15">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="F15" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="28" x14ac:dyDescent="0.3">
-      <c r="A16" s="27"/>
-      <c r="C16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16">
-        <v>3</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="F16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A17" s="27"/>
-      <c r="C17" t="s">
-        <v>258</v>
-      </c>
-      <c r="D17">
-        <v>5</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="F17" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A18" s="27"/>
-      <c r="C18" t="s">
-        <v>259</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="F18" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A19" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="C19" t="s">
-        <v>260</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="F19" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A20" s="27"/>
-      <c r="C20" t="s">
-        <v>261</v>
-      </c>
-      <c r="D20">
-        <v>3</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="F20" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A21" s="27"/>
-      <c r="C21" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21">
-        <v>5</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>432</v>
-      </c>
-      <c r="F21" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A22" s="27"/>
-      <c r="C22" t="s">
-        <v>264</v>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="F22" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A23" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C23" t="s">
-        <v>265</v>
-      </c>
-      <c r="D23">
-        <v>4</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="F23" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="56" x14ac:dyDescent="0.3">
-      <c r="A24" s="27"/>
-      <c r="C24" t="s">
-        <v>266</v>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="F24" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
-      <c r="C25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F25" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="C26" t="s">
-        <v>269</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="F26" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="C27" t="s">
-        <v>270</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="F27" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A28" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C28" t="s">
-        <v>271</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="F28" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="C29" t="s">
-        <v>272</v>
-      </c>
-      <c r="D29">
-        <v>4</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="F29" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="28" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="C30" t="s">
-        <v>273</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="F30" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="C31" t="s">
-        <v>421</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="A11:A18"/>
-    <mergeCell ref="A19:A22"/>
-    <mergeCell ref="A23:A27"/>
-    <mergeCell ref="A28:A31"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="A2:A16"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B2:B4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
